--- a/IPRF_data_validation_source.xlsx
+++ b/IPRF_data_validation_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shahfeen.shamsudheen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B07D58-9454-4D1B-A92D-BEECE9C67FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF90340-4E3A-45E4-A2F1-39AAF2B63805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ENTITY" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3563" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3568" uniqueCount="1295">
   <si>
     <t>Entity</t>
   </si>
@@ -3924,13 +3924,22 @@
   </si>
   <si>
     <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Sam Charles</t>
+  </si>
+  <si>
+    <t>sam.charles@aertssen.be</t>
+  </si>
+  <si>
+    <t>Internal Inspector</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3962,6 +3971,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4023,10 +4040,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4056,8 +4074,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="35">
@@ -4775,8 +4795,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B98371B6-A311-44AB-AD95-76BBCCCC842B}" name="T_REQUESTER" displayName="T_REQUESTER" ref="A1:E190" totalsRowShown="0">
-  <autoFilter ref="A1:E190" xr:uid="{B98371B6-A311-44AB-AD95-76BBCCCC842B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B98371B6-A311-44AB-AD95-76BBCCCC842B}" name="T_REQUESTER" displayName="T_REQUESTER" ref="A1:E191" totalsRowShown="0">
+  <autoFilter ref="A1:E191" xr:uid="{B98371B6-A311-44AB-AD95-76BBCCCC842B}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{AB7AEDD2-E5E9-4885-873A-B22FA3ED4E18}" name="DisplayName"/>
     <tableColumn id="2" xr3:uid="{2148C4AC-D6AF-405E-86A8-6892A8FA9C7D}" name="CompanyName"/>
@@ -17661,7 +17681,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425F11BA-7C7F-490C-952D-BC98FDD4E053}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
@@ -20877,10 +20897,30 @@
         <v>738</v>
       </c>
     </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B191" t="s">
+        <v>699</v>
+      </c>
+      <c r="C191" s="17" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D191" t="s">
+        <v>701</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1294</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C191" r:id="rId1" xr:uid="{7F86FD08-C95A-44F5-8C3E-7D4E544607F3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/IPRF_data_validation_source.xlsx
+++ b/IPRF_data_validation_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://partner-integrations.egnyte.com/msoffice/wopi/files/8cc1db3e-3fd0-4efa-9075-f4439633c71f/WOPIServiceId_TP_EGNYTE_PLUS/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{EE501B87-8F24-4659-B249-C810987B7A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91331A46-04D4-46CA-9B26-8214CC5DBDFE}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="8_{EE501B87-8F24-4659-B249-C810987B7A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3D9A245-12C9-4AA5-9F51-A86071E53393}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ENTITY" sheetId="2" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="SUPPLIER" sheetId="10" r:id="rId13"/>
     <sheet name="UNIT" sheetId="14" r:id="rId14"/>
     <sheet name="PRIORITY" sheetId="13" r:id="rId15"/>
+    <sheet name="PARTS PREFERENCE" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3075" uniqueCount="1292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3078" uniqueCount="1295">
   <si>
     <t>Entity</t>
   </si>
@@ -3928,6 +3929,15 @@
   </si>
   <si>
     <t>Service | Maintenance services</t>
+  </si>
+  <si>
+    <t>Parts preference</t>
+  </si>
+  <si>
+    <t>Aftermarket</t>
+  </si>
+  <si>
+    <t>Genuine / OEM</t>
   </si>
 </sst>
 </file>
@@ -4049,7 +4059,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4078,7 +4088,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4087,334 +4096,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="56">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF8ED973"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF8ED973"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF8ED973"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF8ED973"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF145F82"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF145F82"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF145F82"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF145F82"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF145F82"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF145F82"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF145F82"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF145F82"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF145F82"/>
-          <bgColor rgb="FF145F82"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4621,6 +4302,10 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -5056,6 +4741,212 @@
       </font>
       <fill>
         <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF145F82"/>
+          <bgColor rgb="FF145F82"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF145F82"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF145F82"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF145F82"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF145F82"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF145F82"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF145F82"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF145F82"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF145F82"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
         </patternFill>
@@ -5086,6 +4977,124 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF8ED973"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF8ED973"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF8ED973"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF8ED973"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -5185,13 +5194,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D29FADD4-2FCD-43B0-90C5-9B9CB9E9DF3F}" name="T_ENTITY" displayName="T_ENTITY" ref="A1:D9" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47" tableBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D29FADD4-2FCD-43B0-90C5-9B9CB9E9DF3F}" name="T_ENTITY" displayName="T_ENTITY" ref="A1:D9" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44" tableBorderDxfId="43">
   <autoFilter ref="A1:D9" xr:uid="{D29FADD4-2FCD-43B0-90C5-9B9CB9E9DF3F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CA91E58B-4C56-4531-9063-9552261B2DEA}" name="Entity" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{1B052F4D-BC91-4DBA-8F1D-0FBDD7ADDD24}" name="Entity name" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{2A93B648-FDCB-4D3E-9DF9-7A65A0300628}" name="BU" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{18B10786-38F6-4013-9BC2-F3180D33587F}" name="BU Name" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{CA91E58B-4C56-4531-9063-9552261B2DEA}" name="Entity" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{1B052F4D-BC91-4DBA-8F1D-0FBDD7ADDD24}" name="Entity name" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{2A93B648-FDCB-4D3E-9DF9-7A65A0300628}" name="BU" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{18B10786-38F6-4013-9BC2-F3180D33587F}" name="BU Name" dataDxfId="39"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5215,46 +5224,46 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0575A436-E491-45AF-9764-1EF6316DBE0B}" name="T_BUYER" displayName="T_BUYER" ref="A1:E14" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0575A436-E491-45AF-9764-1EF6316DBE0B}" name="T_BUYER" displayName="T_BUYER" ref="A1:E14" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="A1:E14" xr:uid="{0575A436-E491-45AF-9764-1EF6316DBE0B}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E13">
     <sortCondition ref="E2:E14"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E1BB6612-4F23-4EED-B8F1-CF5982BA1DF6}" name="DisplayName" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{5B4E8BEE-5F8B-4F64-84D8-F88F07C4ABC6}" name="CompanyName" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{3C6CD560-2073-412C-8C06-7169BE0B16B2}" name="EmailAddress" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{D306573A-5DB7-41D7-9B48-D59A3446CD7B}" name="OfficeLocation" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{7288F768-73F4-495F-9081-0E3E82827FBC}" name="JobTitle" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{E1BB6612-4F23-4EED-B8F1-CF5982BA1DF6}" name="DisplayName" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{5B4E8BEE-5F8B-4F64-84D8-F88F07C4ABC6}" name="CompanyName" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{3C6CD560-2073-412C-8C06-7169BE0B16B2}" name="EmailAddress" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{D306573A-5DB7-41D7-9B48-D59A3446CD7B}" name="OfficeLocation" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{7288F768-73F4-495F-9081-0E3E82827FBC}" name="JobTitle" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{20085DC5-67FF-4D75-83A9-B2F934272667}" name="T_INV_WAREHOUSE" displayName="T_INV_WAREHOUSE" ref="A1:F3" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{20085DC5-67FF-4D75-83A9-B2F934272667}" name="T_INV_WAREHOUSE" displayName="T_INV_WAREHOUSE" ref="A1:F3" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:F3" xr:uid="{20085DC5-67FF-4D75-83A9-B2F934272667}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{063B5733-8CBE-40C9-BFA6-CC023954234E}" name="Inventory_Warehouse" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{063B5733-8CBE-40C9-BFA6-CC023954234E}" name="Inventory_Warehouse" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(" | ",TRUE,T_INV_WAREHOUSE[[#This Row],[BU]:[WAREHOUSE NAME]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{65BE572E-2B7D-4595-AFF7-33BF61E79537}" name="BU" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{1DCC7F62-C44E-4E29-A27C-8EC84B91DDDA}" name="COUNTRY" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{0BF556F6-42A4-4428-BA6F-E9562AEBE60F}" name="PROVINCE" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{F329687B-B73A-4C6F-BBCD-2E228417E205}" name="LOCATION_SITE" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{0BD35289-9B86-4DD1-BA28-0B042B4593D9}" name="WAREHOUSE NAME" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{65BE572E-2B7D-4595-AFF7-33BF61E79537}" name="BU" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{1DCC7F62-C44E-4E29-A27C-8EC84B91DDDA}" name="COUNTRY" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{0BF556F6-42A4-4428-BA6F-E9562AEBE60F}" name="PROVINCE" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{F329687B-B73A-4C6F-BBCD-2E228417E205}" name="LOCATION_SITE" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{0BD35289-9B86-4DD1-BA28-0B042B4593D9}" name="WAREHOUSE NAME" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{02D1AE26-0463-4617-B52B-DBF97AAB8203}" name="T_Unit" displayName="T_Unit" ref="A1:C25" totalsRowShown="0" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{02D1AE26-0463-4617-B52B-DBF97AAB8203}" name="T_Unit" displayName="T_Unit" ref="A1:C25" totalsRowShown="0" dataDxfId="3">
   <autoFilter ref="A1:C25" xr:uid="{02D1AE26-0463-4617-B52B-DBF97AAB8203}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{68271648-164A-42D5-826D-4F9733A33380}" name="Unit" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{F880A502-862C-41DB-BE88-5145BECDC8AF}" name="Description" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{051BA3D3-B21A-4AAA-9BF1-CCC4C9F25CFB}" name="Translated description" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{68271648-164A-42D5-826D-4F9733A33380}" name="Unit" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{F880A502-862C-41DB-BE88-5145BECDC8AF}" name="Description" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{051BA3D3-B21A-4AAA-9BF1-CCC4C9F25CFB}" name="Translated description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5273,36 +5282,46 @@
 </table>
 </file>
 
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{AE77B7CD-CCF7-419C-9282-C1F24FBF0CDC}" name="T_Parts_preference1" displayName="T_Parts_preference1" ref="A1:A3" totalsRowShown="0">
+  <autoFilter ref="A1:A3" xr:uid="{AE77B7CD-CCF7-419C-9282-C1F24FBF0CDC}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{334FFF0A-A9DC-4102-AFF4-25DD0F31C05C}" name="Parts preference"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{65FB7794-9EED-445F-BD63-82762A77D442}" name="T_REQTYPE_ITMTYPE_PRIORITY" displayName="T_REQTYPE_ITMTYPE_PRIORITY" ref="A1:C26" totalsRowShown="0">
   <autoFilter ref="A1:C26" xr:uid="{65FB7794-9EED-445F-BD63-82762A77D442}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C1D8B4D3-3614-4E08-AD3C-F478F2F2C52C}" name="Request type" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{86564106-2B13-40CC-B925-68F3D0AE7525}" name="Item type" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{35311A1E-833D-4D17-B28A-08F850525D4F}" name="Priority" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C1D8B4D3-3614-4E08-AD3C-F478F2F2C52C}" name="Request type" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{86564106-2B13-40CC-B925-68F3D0AE7525}" name="Item type" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{35311A1E-833D-4D17-B28A-08F850525D4F}" name="Priority" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7 2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BA46386E-07FD-4161-B330-FAD82FFD47E3}" name="T_ENTITY_BU" displayName="T_ENTITY_BU" ref="A1:D9" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BA46386E-07FD-4161-B330-FAD82FFD47E3}" name="T_ENTITY_BU" displayName="T_ENTITY_BU" ref="A1:D9" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" tableBorderDxfId="36">
   <autoFilter ref="A1:D9" xr:uid="{D29FADD4-2FCD-43B0-90C5-9B9CB9E9DF3F}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{47146366-C69B-4D36-A325-0517C11BF38E}" name="Entity" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{0C482FEB-E0BB-4E9A-84BE-F627D850D846}" name="Entity name" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1BB790E8-A241-4340-A0C5-E2D415378DE2}" name="BU" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{C15A61C7-5943-4D2F-95E9-497F631FD65B}" name="BU Name" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{47146366-C69B-4D36-A325-0517C11BF38E}" name="Entity" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{0C482FEB-E0BB-4E9A-84BE-F627D850D846}" name="Entity name" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{1BB790E8-A241-4340-A0C5-E2D415378DE2}" name="BU" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{C15A61C7-5943-4D2F-95E9-497F631FD65B}" name="BU Name" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4EB3F7BF-B15F-49CA-96FB-709128A5DDA3}" name="T_BU" displayName="T_BU" ref="A1:A5" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4EB3F7BF-B15F-49CA-96FB-709128A5DDA3}" name="T_BU" displayName="T_BU" ref="A1:A5" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" tableBorderDxfId="29">
   <autoFilter ref="A1:A5" xr:uid="{4EB3F7BF-B15F-49CA-96FB-709128A5DDA3}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{5B4E2800-3EB0-409F-9845-1F80CEABE14A}" name="Business Unit" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{5B4E2800-3EB0-409F-9845-1F80CEABE14A}" name="Business Unit" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5319,12 +5338,12 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{373C561D-71B0-431B-9DC9-BF9AAA414574}" name="T_ITEM_TYPE" displayName="T_ITEM_TYPE" ref="A1:C7" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36" tableBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{373C561D-71B0-431B-9DC9-BF9AAA414574}" name="T_ITEM_TYPE" displayName="T_ITEM_TYPE" ref="A1:C7" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26" tableBorderDxfId="25">
   <autoFilter ref="A1:C7" xr:uid="{373C561D-71B0-431B-9DC9-BF9AAA414574}"/>
   <tableColumns count="3">
-    <tableColumn id="3" xr3:uid="{28CFE494-0E58-43EF-B2D5-9008C628E156}" name="Item type - Primary" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{B435490A-C8D3-4764-B264-F7012AB79190}" name="Item type - Secondary" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{1A2937A1-7561-4788-B8C0-A958B1FE0FB3}" name="Item type" dataDxfId="32">
+    <tableColumn id="3" xr3:uid="{28CFE494-0E58-43EF-B2D5-9008C628E156}" name="Item type - Primary" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{B435490A-C8D3-4764-B264-F7012AB79190}" name="Item type - Secondary" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{1A2937A1-7561-4788-B8C0-A958B1FE0FB3}" name="Item type" dataDxfId="22">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(" | ", TRUE,T_ITEM_TYPE[[#This Row],[Item type - Primary]],T_ITEM_TYPE[[#This Row],[Item type - Secondary]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5337,7 +5356,7 @@
   <autoFilter ref="A1:H247" xr:uid="{B6A202E1-A28D-4809-9897-01651B068C20}"/>
   <tableColumns count="8">
     <tableColumn id="2" xr3:uid="{6BAD475D-6FF7-4626-9D8A-DB7360DBFE88}" name="ProjectID"/>
-    <tableColumn id="7" xr3:uid="{19CFDC38-4EB6-4779-9E14-6E5BBB7B8174}" name="ProjectID Abb" dataDxfId="31">
+    <tableColumn id="7" xr3:uid="{19CFDC38-4EB6-4779-9E14-6E5BBB7B8174}" name="ProjectID Abb" dataDxfId="21">
       <calculatedColumnFormula>IF(OR(LEFT(T_PROJECTS[[#This Row],[ProjectID]],4)="J000",LEFT(T_PROJECTS[[#This Row],[ProjectID]],4)="R000"),
 LEFT(T_PROJECTS[[#This Row],[ProjectID]],1)&amp;VALUE(MID(T_PROJECTS[[#This Row],[ProjectID]],2,99)),
 "")</calculatedColumnFormula>
@@ -5347,7 +5366,7 @@
     <tableColumn id="3" xr3:uid="{96AB9E8F-85EB-4109-AAD0-ADAEADF74CE7}" name="DimensionDisplayValue"/>
     <tableColumn id="4" xr3:uid="{BFE2CBA2-A2CB-4B2F-A5BC-33C930D6E068}" name="ParentProject"/>
     <tableColumn id="5" xr3:uid="{1E2C2E12-E303-4694-939D-961A89E2C6BE}" name="ProjectStage"/>
-    <tableColumn id="8" xr3:uid="{12679CB7-F970-42EE-8C81-813F1842A34C}" name="ProjectID_Name" dataDxfId="30">
+    <tableColumn id="8" xr3:uid="{12679CB7-F970-42EE-8C81-813F1842A34C}" name="ProjectID_Name" dataDxfId="20">
       <calculatedColumnFormula>_xlfn.TEXTJOIN(" | ", TRUE, T_PROJECTS[[#This Row],[ProjectID]], T_PROJECTS[[#This Row],[ProjectName]],T_PROJECTS[[#This Row],[ProjectID Abb]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5383,7 +5402,7 @@
     <tableColumn id="3" xr3:uid="{75F4F8AB-B912-4977-A92F-5AD620717A38}" name="EmailAddress"/>
     <tableColumn id="4" xr3:uid="{BD96EFCF-BB07-47E2-BB09-E06FA5614FB2}" name="OfficeLocation"/>
     <tableColumn id="5" xr3:uid="{35DB8EAA-8EC5-4711-8A0F-B3C2892830E3}" name="JobTitle"/>
-    <tableColumn id="6" xr3:uid="{0986A8E3-152B-4570-ABC0-260BD8DB8699}" name="Request Prefix" dataDxfId="10">
+    <tableColumn id="6" xr3:uid="{0986A8E3-152B-4570-ABC0-260BD8DB8699}" name="Request Prefix" dataDxfId="19">
       <calculatedColumnFormula>_xlfn.LET(
     _xlpm.fullName, TRIM(T_REQUESTER[[#This Row],[DisplayName]]),
     _xlpm.firstName, LEFT(_xlpm.fullName, FIND(" ", _xlpm.fullName &amp; " ") - 1),
@@ -6452,15 +6471,15 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="8" t="s">
         <v>1283</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8" t="s">
         <v>1283</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6900,6 +6919,38 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462A1636-8A1E-4BD0-A75E-3EC9B7AD2E27}">
+  <sheetPr codeName="Sheet16"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BB3374B-B408-4017-86CF-BC923BB47703}">
   <sheetPr codeName="Sheet15"/>
@@ -6923,277 +6974,277 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>1287</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>1269</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>1287</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>1287</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>1271</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>1287</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>1288</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>1269</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>1288</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>1288</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>1271</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>1288</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>1289</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>1289</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>1290</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>1290</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>1291</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>1269</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>1291</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>1291</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>1287</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>1287</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>1288</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>1288</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>1290</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>1290</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>1291</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>1270</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>1291</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>1272</v>
       </c>
     </row>
